--- a/docs/tech/ezApproval/전자결재_TYPES_정리문서(21.01.21).xlsx
+++ b/docs/tech/ezApproval/전자결재_TYPES_정리문서(21.01.21).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MINSEONG\git\ezFlow4Java\docs\tech\ezApproval\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3E78D0D-7B25-462E-8D80-FDEA36088BCC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FF6E4A9-A7AD-44E3-A8F5-5D9FE1B10A4E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="123">
   <si>
     <t>전자결재TYPES</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -434,10 +434,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>J</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>N</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -466,23 +462,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>도착</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>시스템삭제</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>전송실패</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>접수</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>지정</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1171,10 +1155,8 @@
       <c r="H7" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I7" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="J7" s="13"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="2"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
@@ -1201,12 +1183,10 @@
       <c r="H8" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>115</v>
-      </c>
+      <c r="I8" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="J8" s="13"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
@@ -1234,10 +1214,10 @@
         <v>49</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>116</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
@@ -1266,10 +1246,10 @@
         <v>55</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
@@ -1296,10 +1276,10 @@
         <v>62</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>80</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -1328,10 +1308,10 @@
         <v>68</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>118</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
@@ -1360,10 +1340,10 @@
         <v>72</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>119</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
@@ -1392,10 +1372,10 @@
         <v>76</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
@@ -1424,10 +1404,10 @@
         <v>80</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
@@ -1456,10 +1436,10 @@
         <v>85</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
@@ -1488,10 +1468,10 @@
         <v>89</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
@@ -1520,10 +1500,10 @@
         <v>93</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
@@ -1548,10 +1528,10 @@
         <v>97</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
@@ -1572,10 +1552,10 @@
       <c r="G20" s="3"/>
       <c r="H20" s="2"/>
       <c r="I20" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -1588,7 +1568,7 @@
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="I2:J2"/>
-    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="I8:J8"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
